--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -1507,7 +1507,7 @@
     <t>0.0509,0.0169,0.9339,0.0071</t>
   </si>
   <si>
-    <t>0.7669,0.0008,0.2375,0.0022</t>
+    <t>0.7669,0.0008,0.2374,0.0022</t>
   </si>
   <si>
     <t>0.3069,0.0007,0.6604,0.0087</t>

--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_5/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
   <si>
     <t>Filename</t>
   </si>
@@ -817,6 +817,9 @@
     <t>0,0,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,0,0</t>
   </si>
   <si>
@@ -826,19 +829,22 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9207,0.0024,0.0232,0.0113</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9203,0.0024,0.0233,0.0113</t>
   </si>
   <si>
     <t>0.0041,0.0007,0.0004,0.9992</t>
   </si>
   <si>
-    <t>0.9293,0.0009,0.0005,0.0349</t>
-  </si>
-  <si>
-    <t>0.1026,0.0005,0.0026,0.9641</t>
-  </si>
-  <si>
-    <t>0.9932,0.0017,0.0017,0.0003</t>
+    <t>0.9292,0.0009,0.0005,0.0350</t>
+  </si>
+  <si>
+    <t>0.1026,0.0005,0.0027,0.9640</t>
+  </si>
+  <si>
+    <t>0.9932,0.0017,0.0018,0.0003</t>
   </si>
   <si>
     <t>0.9897,0.0067,0.0016,0.0007</t>
@@ -847,10 +853,10 @@
     <t>0.9883,0.0028,0.0037,0.0003</t>
   </si>
   <si>
-    <t>0.9921,0.0020,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.9608,0.0460,0.0004,0.0005</t>
+    <t>0.9920,0.0020,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.9608,0.0461,0.0005,0.0005</t>
   </si>
   <si>
     <t>0.9864,0.0105,0.0022,0.0010</t>
@@ -862,19 +868,19 @@
     <t>0.9921,0.0023,0.0019,0.0003</t>
   </si>
   <si>
-    <t>0.7291,0.0050,0.2531,0.0048</t>
+    <t>0.7275,0.0049,0.2549,0.0048</t>
   </si>
   <si>
     <t>0.0168,0.0106,0.9792,0.0022</t>
   </si>
   <si>
-    <t>0.2669,0.0006,0.8418,0.0002</t>
-  </si>
-  <si>
-    <t>0.0547,0.0030,0.9552,0.0021</t>
-  </si>
-  <si>
-    <t>0.5802,0.0005,0.5296,0.0005</t>
+    <t>0.2665,0.0006,0.8422,0.0002</t>
+  </si>
+  <si>
+    <t>0.0546,0.0030,0.9554,0.0021</t>
+  </si>
+  <si>
+    <t>0.5785,0.0005,0.5317,0.0005</t>
   </si>
   <si>
     <t>0.0008,0.9988,0.0059,0.0012</t>
@@ -886,139 +892,139 @@
     <t>0.0090,0.9962,0.0024,0.0001</t>
   </si>
   <si>
-    <t>0.0038,0.9950,0.0074,0.0034</t>
+    <t>0.0038,0.9950,0.0075,0.0035</t>
   </si>
   <si>
     <t>0.0008,0.9993,0.0058,0.0003</t>
   </si>
   <si>
-    <t>0.3292,0.0010,0.7099,0.0028</t>
-  </si>
-  <si>
-    <t>0.0628,0.0105,0.9198,0.0089</t>
-  </si>
-  <si>
-    <t>0.0162,0.0002,0.9911,0.0003</t>
-  </si>
-  <si>
-    <t>0.0221,0.0014,0.9825,0.0014</t>
-  </si>
-  <si>
-    <t>0.0142,0.0006,0.9903,0.0009</t>
-  </si>
-  <si>
-    <t>0.0336,0.0002,0.9812,0.0004</t>
+    <t>0.3281,0.0010,0.7111,0.0028</t>
+  </si>
+  <si>
+    <t>0.0624,0.0105,0.9203,0.0089</t>
+  </si>
+  <si>
+    <t>0.0162,0.0002,0.9912,0.0003</t>
+  </si>
+  <si>
+    <t>0.0220,0.0014,0.9826,0.0014</t>
+  </si>
+  <si>
+    <t>0.0141,0.0006,0.9904,0.0009</t>
+  </si>
+  <si>
+    <t>0.0335,0.0002,0.9813,0.0004</t>
   </si>
   <si>
     <t>0.0078,0.0001,0.9954,0.0003</t>
   </si>
   <si>
-    <t>0.6412,0.2914,0.0354,0.0044</t>
-  </si>
-  <si>
-    <t>0.9421,0.0577,0.0033,0.0015</t>
+    <t>0.6413,0.2908,0.0357,0.0044</t>
+  </si>
+  <si>
+    <t>0.9420,0.0579,0.0033,0.0015</t>
   </si>
   <si>
     <t>0.0019,0.0006,0.9987,0.0004</t>
   </si>
   <si>
-    <t>0.0180,0.0860,0.9031,0.0015</t>
-  </si>
-  <si>
-    <t>0.9446,0.0054,0.0250,0.0014</t>
-  </si>
-  <si>
-    <t>0.9121,0.0228,0.0358,0.0016</t>
-  </si>
-  <si>
-    <t>0.3832,0.6853,0.0230,0.0039</t>
-  </si>
-  <si>
-    <t>0.0051,0.9360,0.6680,0.0018</t>
-  </si>
-  <si>
-    <t>0.0004,0.5636,0.9908,0.0001</t>
+    <t>0.0180,0.0857,0.9035,0.0015</t>
+  </si>
+  <si>
+    <t>0.9443,0.0054,0.0253,0.0014</t>
+  </si>
+  <si>
+    <t>0.9117,0.0227,0.0361,0.0016</t>
+  </si>
+  <si>
+    <t>0.3830,0.6854,0.0232,0.0039</t>
+  </si>
+  <si>
+    <t>0.0051,0.9357,0.6691,0.0018</t>
+  </si>
+  <si>
+    <t>0.0004,0.5637,0.9908,0.0001</t>
   </si>
   <si>
     <t>0.0038,0.0013,0.9960,0.0006</t>
   </si>
   <si>
-    <t>0.0391,0.0170,0.9397,0.0032</t>
-  </si>
-  <si>
-    <t>0.0549,0.0009,0.9414,0.0108</t>
-  </si>
-  <si>
-    <t>0.0009,0.2779,0.9864,0.0005</t>
-  </si>
-  <si>
-    <t>0.0040,0.9941,0.0100,0.0004</t>
-  </si>
-  <si>
-    <t>0.0058,0.0067,0.9901,0.0010</t>
-  </si>
-  <si>
-    <t>0.0008,0.8183,0.0006,0.9277</t>
+    <t>0.0391,0.0170,0.9398,0.0032</t>
+  </si>
+  <si>
+    <t>0.0545,0.0009,0.9419,0.0107</t>
+  </si>
+  <si>
+    <t>0.0009,0.2776,0.9865,0.0005</t>
+  </si>
+  <si>
+    <t>0.0040,0.9940,0.0100,0.0004</t>
+  </si>
+  <si>
+    <t>0.0058,0.0067,0.9902,0.0010</t>
+  </si>
+  <si>
+    <t>0.0008,0.8186,0.0006,0.9277</t>
   </si>
   <si>
     <t>0.0001,0.9999,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.0003,0.9995,0.0346,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0075,0.0001</t>
+    <t>0.0003,0.9995,0.0348,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0076,0.0001</t>
   </si>
   <si>
     <t>0.0002,0.0064,0.9991,0.0002</t>
   </si>
   <si>
-    <t>0.0012,0.2419,0.9836,0.0014</t>
-  </si>
-  <si>
-    <t>0.0076,0.0010,0.9924,0.0013</t>
-  </si>
-  <si>
-    <t>0.0238,0.0000,0.9919,0.0001</t>
-  </si>
-  <si>
-    <t>0.0122,0.0013,0.9907,0.0006</t>
+    <t>0.0012,0.2418,0.9837,0.0014</t>
+  </si>
+  <si>
+    <t>0.0076,0.0010,0.9925,0.0013</t>
+  </si>
+  <si>
+    <t>0.0237,0.0000,0.9920,0.0001</t>
+  </si>
+  <si>
+    <t>0.0122,0.0013,0.9908,0.0006</t>
   </si>
   <si>
     <t>0.0170,0.0151,0.9632,0.0042</t>
   </si>
   <si>
-    <t>0.9589,0.0156,0.0161,0.0013</t>
-  </si>
-  <si>
-    <t>0.9706,0.0010,0.0196,0.0003</t>
-  </si>
-  <si>
-    <t>0.9661,0.0143,0.0103,0.0059</t>
-  </si>
-  <si>
-    <t>0.1927,0.0015,0.8591,0.0012</t>
-  </si>
-  <si>
-    <t>0.9833,0.0008,0.0084,0.0002</t>
-  </si>
-  <si>
-    <t>0.9876,0.0018,0.0048,0.0006</t>
-  </si>
-  <si>
-    <t>0.9875,0.0019,0.0048,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9965,0.8560,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0239,0.9985,0.0001</t>
+    <t>0.9587,0.0156,0.0162,0.0013</t>
+  </si>
+  <si>
+    <t>0.9704,0.0010,0.0198,0.0003</t>
+  </si>
+  <si>
+    <t>0.9660,0.0143,0.0104,0.0059</t>
+  </si>
+  <si>
+    <t>0.1918,0.0015,0.8601,0.0012</t>
+  </si>
+  <si>
+    <t>0.9832,0.0008,0.0085,0.0002</t>
+  </si>
+  <si>
+    <t>0.9875,0.0018,0.0049,0.0006</t>
+  </si>
+  <si>
+    <t>0.9874,0.0019,0.0049,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9965,0.8563,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0238,0.9985,0.0001</t>
   </si>
   <si>
     <t>0.0020,0.0088,0.9948,0.0009</t>
   </si>
   <si>
-    <t>0.0003,0.9842,0.8327,0.0005</t>
+    <t>0.0003,0.9842,0.8329,0.0005</t>
   </si>
   <si>
     <t>0.0001,0.0000,0.9999,0.0001</t>
@@ -1030,28 +1036,28 @@
     <t>0.0004,0.9996,0.0014,0.0000</t>
   </si>
   <si>
-    <t>0.9411,0.0006,0.0496,0.0002</t>
-  </si>
-  <si>
-    <t>0.1570,0.0528,0.8184,0.0064</t>
-  </si>
-  <si>
-    <t>0.0198,0.0073,0.9844,0.0018</t>
-  </si>
-  <si>
-    <t>0.0007,0.9508,0.8979,0.0007</t>
-  </si>
-  <si>
-    <t>0.0006,0.8148,0.9727,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.1158,0.0000</t>
+    <t>0.9407,0.0006,0.0501,0.0002</t>
+  </si>
+  <si>
+    <t>0.1562,0.0526,0.8195,0.0064</t>
+  </si>
+  <si>
+    <t>0.0198,0.0073,0.9845,0.0018</t>
+  </si>
+  <si>
+    <t>0.0007,0.9507,0.8981,0.0007</t>
+  </si>
+  <si>
+    <t>0.0006,0.8145,0.9727,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.1161,0.0000</t>
   </si>
   <si>
     <t>0.0003,0.9299,0.9464,0.0006</t>
   </si>
   <si>
-    <t>0.0026,0.0009,0.0026,0.9991</t>
+    <t>0.0026,0.0009,0.0027,0.9991</t>
   </si>
   <si>
     <t>0.0003,0.0008,0.0003,0.9999</t>
@@ -1069,31 +1075,31 @@
     <t>0.0001,0.0004,0.0025,0.9999</t>
   </si>
   <si>
-    <t>0.0002,0.9945,0.8649,0.0001</t>
+    <t>0.0002,0.9945,0.8651,0.0001</t>
   </si>
   <si>
     <t>0.0005,0.6687,0.9841,0.0003</t>
   </si>
   <si>
-    <t>0.0019,0.9597,0.5480,0.0011</t>
-  </si>
-  <si>
-    <t>0.0005,0.7572,0.9832,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.9923,0.9227,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9953,0.3596,0.0003</t>
+    <t>0.0019,0.9596,0.5492,0.0011</t>
+  </si>
+  <si>
+    <t>0.0005,0.7569,0.9832,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9923,0.9228,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.9953,0.3606,0.0003</t>
   </si>
   <si>
     <t>0.9920,0.0079,0.0007,0.0004</t>
   </si>
   <si>
-    <t>0.9759,0.0189,0.0044,0.0010</t>
-  </si>
-  <si>
-    <t>0.9639,0.0516,0.0014,0.0005</t>
+    <t>0.9758,0.0189,0.0044,0.0010</t>
+  </si>
+  <si>
+    <t>0.9639,0.0517,0.0014,0.0005</t>
   </si>
   <si>
     <t>0.9902,0.0114,0.0009,0.0004</t>
@@ -1105,31 +1111,31 @@
     <t>0.9932,0.0042,0.0011,0.0012</t>
   </si>
   <si>
-    <t>0.9824,0.0029,0.0062,0.0007</t>
-  </si>
-  <si>
-    <t>0.9798,0.0044,0.0038,0.0021</t>
+    <t>0.9823,0.0029,0.0063,0.0007</t>
+  </si>
+  <si>
+    <t>0.9797,0.0044,0.0038,0.0021</t>
   </si>
   <si>
     <t>0.9911,0.0013,0.0027,0.0005</t>
   </si>
   <si>
-    <t>0.9880,0.0092,0.0022,0.0010</t>
+    <t>0.9879,0.0092,0.0022,0.0010</t>
   </si>
   <si>
     <t>0.9953,0.0022,0.0007,0.0002</t>
   </si>
   <si>
-    <t>0.9936,0.0031,0.0010,0.0006</t>
-  </si>
-  <si>
-    <t>0.9880,0.0075,0.0018,0.0011</t>
+    <t>0.9935,0.0031,0.0010,0.0006</t>
+  </si>
+  <si>
+    <t>0.9880,0.0076,0.0018,0.0011</t>
   </si>
   <si>
     <t>0.9950,0.0027,0.0008,0.0008</t>
   </si>
   <si>
-    <t>0.9951,0.0029,0.0006,0.0004</t>
+    <t>0.9950,0.0029,0.0006,0.0004</t>
   </si>
   <si>
     <t>0.9931,0.0021,0.0014,0.0003</t>
@@ -1138,19 +1144,19 @@
     <t>0.0020,0.0001,0.9990,0.0001</t>
   </si>
   <si>
-    <t>0.0233,0.0024,0.9807,0.0021</t>
-  </si>
-  <si>
-    <t>0.9569,0.0001,0.0505,0.0003</t>
-  </si>
-  <si>
-    <t>0.0460,0.0021,0.9574,0.0015</t>
-  </si>
-  <si>
-    <t>0.3329,0.7305,0.0035,0.0015</t>
-  </si>
-  <si>
-    <t>0.0798,0.9289,0.0432,0.0097</t>
+    <t>0.0232,0.0024,0.9808,0.0021</t>
+  </si>
+  <si>
+    <t>0.9567,0.0001,0.0509,0.0003</t>
+  </si>
+  <si>
+    <t>0.0458,0.0021,0.9576,0.0014</t>
+  </si>
+  <si>
+    <t>0.3323,0.7312,0.0036,0.0015</t>
+  </si>
+  <si>
+    <t>0.0797,0.9289,0.0434,0.0097</t>
   </si>
   <si>
     <t>0.0002,0.9999,0.0003,0.0001</t>
@@ -1159,22 +1165,22 @@
     <t>0.0000,1.0000,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.6687,0.3280,0.0501,0.0044</t>
-  </si>
-  <si>
-    <t>0.1712,0.0262,0.8159,0.0131</t>
-  </si>
-  <si>
-    <t>0.0460,0.0068,0.9506,0.0051</t>
-  </si>
-  <si>
-    <t>0.2717,0.0064,0.7213,0.0043</t>
-  </si>
-  <si>
-    <t>0.1361,0.0140,0.8590,0.0129</t>
-  </si>
-  <si>
-    <t>0.0003,0.5302,0.4891,0.3477</t>
+    <t>0.6682,0.3282,0.0505,0.0044</t>
+  </si>
+  <si>
+    <t>0.1703,0.0261,0.8172,0.0130</t>
+  </si>
+  <si>
+    <t>0.0459,0.0068,0.9508,0.0051</t>
+  </si>
+  <si>
+    <t>0.2707,0.0064,0.7225,0.0042</t>
+  </si>
+  <si>
+    <t>0.1352,0.0140,0.8600,0.0128</t>
+  </si>
+  <si>
+    <t>0.0003,0.5294,0.4909,0.3461</t>
   </si>
   <si>
     <t>0.0001,0.9999,0.0016,0.0000</t>
@@ -1186,67 +1192,67 @@
     <t>0.0001,0.9994,0.0004,0.0055</t>
   </si>
   <si>
-    <t>0.0002,0.9991,0.0459,0.0004</t>
-  </si>
-  <si>
-    <t>0.0026,0.9892,0.2867,0.0013</t>
-  </si>
-  <si>
-    <t>0.2608,0.6642,0.1096,0.0062</t>
-  </si>
-  <si>
-    <t>0.2163,0.6791,0.1719,0.0190</t>
-  </si>
-  <si>
-    <t>0.9816,0.0009,0.0051,0.0008</t>
+    <t>0.0002,0.9991,0.0461,0.0004</t>
+  </si>
+  <si>
+    <t>0.0026,0.9891,0.2878,0.0013</t>
+  </si>
+  <si>
+    <t>0.2600,0.6635,0.1105,0.0062</t>
+  </si>
+  <si>
+    <t>0.2157,0.6789,0.1732,0.0190</t>
+  </si>
+  <si>
+    <t>0.9815,0.0009,0.0051,0.0008</t>
   </si>
   <si>
     <t>0.9892,0.0050,0.0005,0.0013</t>
   </si>
   <si>
-    <t>0.9890,0.0056,0.0018,0.0011</t>
-  </si>
-  <si>
-    <t>0.9870,0.0018,0.0043,0.0009</t>
-  </si>
-  <si>
-    <t>0.9889,0.0045,0.0022,0.0021</t>
-  </si>
-  <si>
-    <t>0.9754,0.0012,0.0092,0.0006</t>
+    <t>0.9890,0.0057,0.0019,0.0011</t>
+  </si>
+  <si>
+    <t>0.9869,0.0018,0.0044,0.0009</t>
+  </si>
+  <si>
+    <t>0.9888,0.0045,0.0022,0.0021</t>
+  </si>
+  <si>
+    <t>0.9753,0.0012,0.0092,0.0006</t>
   </si>
   <si>
     <t>0.9931,0.0017,0.0015,0.0004</t>
   </si>
   <si>
-    <t>0.9929,0.0011,0.0019,0.0003</t>
-  </si>
-  <si>
-    <t>0.0010,0.7489,0.9666,0.0006</t>
-  </si>
-  <si>
-    <t>0.0005,0.3801,0.9918,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0199,0.9973,0.0003</t>
+    <t>0.9928,0.0011,0.0019,0.0003</t>
+  </si>
+  <si>
+    <t>0.0010,0.7487,0.9666,0.0006</t>
+  </si>
+  <si>
+    <t>0.0005,0.3798,0.9919,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0198,0.9973,0.0003</t>
   </si>
   <si>
     <t>0.0096,0.0055,0.9910,0.0003</t>
   </si>
   <si>
-    <t>0.9363,0.0011,0.0390,0.0019</t>
-  </si>
-  <si>
-    <t>0.3457,0.3875,0.0656,0.0107</t>
-  </si>
-  <si>
-    <t>0.1719,0.0002,0.8952,0.0012</t>
-  </si>
-  <si>
-    <t>0.4742,0.0064,0.4931,0.0075</t>
-  </si>
-  <si>
-    <t>0.0115,0.0001,0.0012,0.9971</t>
+    <t>0.9360,0.0011,0.0393,0.0019</t>
+  </si>
+  <si>
+    <t>0.3456,0.3862,0.0662,0.0107</t>
+  </si>
+  <si>
+    <t>0.1713,0.0002,0.8957,0.0012</t>
+  </si>
+  <si>
+    <t>0.4725,0.0064,0.4951,0.0075</t>
+  </si>
+  <si>
+    <t>0.0115,0.0001,0.0013,0.9971</t>
   </si>
   <si>
     <t>0.0000,0.0003,0.0004,1.0000</t>
@@ -1258,19 +1264,19 @@
     <t>0.0033,0.0002,0.0015,0.9993</t>
   </si>
   <si>
-    <t>0.0002,0.9930,0.8137,0.0002</t>
-  </si>
-  <si>
-    <t>0.9836,0.0016,0.0058,0.0006</t>
-  </si>
-  <si>
-    <t>0.0118,0.9842,0.0174,0.0137</t>
+    <t>0.0002,0.9930,0.8139,0.0002</t>
+  </si>
+  <si>
+    <t>0.9835,0.0016,0.0059,0.0006</t>
+  </si>
+  <si>
+    <t>0.0118,0.9841,0.0175,0.0137</t>
   </si>
   <si>
     <t>0.9908,0.0010,0.0029,0.0002</t>
   </si>
   <si>
-    <t>0.0284,0.9774,0.0131,0.0023</t>
+    <t>0.0285,0.9773,0.0132,0.0023</t>
   </si>
   <si>
     <t>0.9905,0.0009,0.0017,0.0013</t>
@@ -1279,52 +1285,52 @@
     <t>0.0024,0.0000,0.9995,0.0000</t>
   </si>
   <si>
-    <t>0.0223,0.0000,0.9942,0.0000</t>
+    <t>0.0221,0.0000,0.9942,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.7031,0.0000,0.1434,0.0024</t>
-  </si>
-  <si>
-    <t>0.9845,0.0031,0.0038,0.0005</t>
-  </si>
-  <si>
-    <t>0.7294,0.1116,0.0715,0.0026</t>
-  </si>
-  <si>
-    <t>0.9833,0.0023,0.0058,0.0008</t>
-  </si>
-  <si>
-    <t>0.9394,0.0289,0.0176,0.0019</t>
-  </si>
-  <si>
-    <t>0.0585,0.9325,0.0223,0.0124</t>
-  </si>
-  <si>
-    <t>0.8573,0.0588,0.0684,0.0038</t>
-  </si>
-  <si>
-    <t>0.7406,0.0148,0.1797,0.0035</t>
+    <t>0.7019,0.0000,0.1445,0.0024</t>
+  </si>
+  <si>
+    <t>0.9844,0.0031,0.0038,0.0005</t>
+  </si>
+  <si>
+    <t>0.7290,0.1113,0.0722,0.0026</t>
+  </si>
+  <si>
+    <t>0.9832,0.0023,0.0058,0.0008</t>
+  </si>
+  <si>
+    <t>0.9393,0.0288,0.0177,0.0019</t>
+  </si>
+  <si>
+    <t>0.0586,0.9324,0.0224,0.0124</t>
+  </si>
+  <si>
+    <t>0.8568,0.0587,0.0689,0.0038</t>
+  </si>
+  <si>
+    <t>0.7393,0.0148,0.1809,0.0035</t>
   </si>
   <si>
     <t>0.9892,0.0066,0.0019,0.0006</t>
   </si>
   <si>
-    <t>0.9903,0.0069,0.0009,0.0009</t>
-  </si>
-  <si>
-    <t>0.9814,0.0030,0.0071,0.0011</t>
+    <t>0.9903,0.0069,0.0009,0.0010</t>
+  </si>
+  <si>
+    <t>0.9813,0.0030,0.0071,0.0011</t>
   </si>
   <si>
     <t>0.9881,0.0012,0.0037,0.0004</t>
   </si>
   <si>
-    <t>0.9885,0.0033,0.0030,0.0004</t>
-  </si>
-  <si>
-    <t>0.9871,0.0076,0.0026,0.0009</t>
+    <t>0.9884,0.0033,0.0030,0.0004</t>
+  </si>
+  <si>
+    <t>0.9871,0.0077,0.0027,0.0009</t>
   </si>
   <si>
     <t>0.9856,0.0048,0.0037,0.0007</t>
@@ -1333,34 +1339,34 @@
     <t>0.9915,0.0021,0.0020,0.0003</t>
   </si>
   <si>
-    <t>0.7394,0.2623,0.0126,0.0077</t>
-  </si>
-  <si>
-    <t>0.2265,0.8078,0.0183,0.0066</t>
-  </si>
-  <si>
-    <t>0.7328,0.3077,0.0021,0.0008</t>
-  </si>
-  <si>
-    <t>0.8960,0.0131,0.0800,0.0016</t>
-  </si>
-  <si>
-    <t>0.9871,0.0070,0.0029,0.0005</t>
-  </si>
-  <si>
-    <t>0.8520,0.0322,0.0947,0.0028</t>
-  </si>
-  <si>
-    <t>0.9846,0.0020,0.0064,0.0004</t>
-  </si>
-  <si>
-    <t>0.9206,0.0678,0.0236,0.0060</t>
+    <t>0.7388,0.2630,0.0127,0.0077</t>
+  </si>
+  <si>
+    <t>0.2262,0.8080,0.0185,0.0066</t>
+  </si>
+  <si>
+    <t>0.7327,0.3079,0.0022,0.0008</t>
+  </si>
+  <si>
+    <t>0.8951,0.0131,0.0810,0.0016</t>
+  </si>
+  <si>
+    <t>0.9870,0.0071,0.0029,0.0005</t>
+  </si>
+  <si>
+    <t>0.8510,0.0323,0.0957,0.0028</t>
+  </si>
+  <si>
+    <t>0.9846,0.0020,0.0065,0.0004</t>
+  </si>
+  <si>
+    <t>0.9204,0.0679,0.0238,0.0060</t>
   </si>
   <si>
     <t>0.0092,0.0049,0.9952,0.0004</t>
   </si>
   <si>
-    <t>0.8474,0.0577,0.0791,0.0024</t>
+    <t>0.8467,0.0576,0.0797,0.0024</t>
   </si>
   <si>
     <t>0.0012,0.0003,0.9991,0.0001</t>
@@ -1369,10 +1375,10 @@
     <t>0.0002,0.1027,0.9959,0.0007</t>
   </si>
   <si>
-    <t>0.0096,0.0018,0.9928,0.0015</t>
-  </si>
-  <si>
-    <t>0.0024,0.1015,0.9860,0.0007</t>
+    <t>0.0096,0.0018,0.9929,0.0015</t>
+  </si>
+  <si>
+    <t>0.0024,0.1014,0.9860,0.0007</t>
   </si>
   <si>
     <t>0.0011,0.0008,0.9991,0.0001</t>
@@ -1384,94 +1390,94 @@
     <t>0.0183,0.0010,0.9860,0.0007</t>
   </si>
   <si>
-    <t>0.1311,0.0038,0.8775,0.0024</t>
-  </si>
-  <si>
-    <t>0.2174,0.0003,0.8662,0.0003</t>
-  </si>
-  <si>
-    <t>0.4595,0.0197,0.4830,0.0083</t>
-  </si>
-  <si>
-    <t>0.0464,0.0083,0.9506,0.0037</t>
-  </si>
-  <si>
-    <t>0.0170,0.0151,0.9703,0.0010</t>
-  </si>
-  <si>
-    <t>0.0744,0.0019,0.9442,0.0012</t>
-  </si>
-  <si>
-    <t>0.1064,0.0051,0.9007,0.0054</t>
-  </si>
-  <si>
-    <t>0.4994,0.0208,0.4407,0.0056</t>
-  </si>
-  <si>
-    <t>0.0598,0.9676,0.0066,0.0004</t>
+    <t>0.1306,0.0038,0.8781,0.0024</t>
+  </si>
+  <si>
+    <t>0.2170,0.0003,0.8666,0.0003</t>
+  </si>
+  <si>
+    <t>0.4575,0.0196,0.4855,0.0082</t>
+  </si>
+  <si>
+    <t>0.0462,0.0083,0.9509,0.0036</t>
+  </si>
+  <si>
+    <t>0.0170,0.0150,0.9704,0.0010</t>
+  </si>
+  <si>
+    <t>0.0742,0.0019,0.9444,0.0012</t>
+  </si>
+  <si>
+    <t>0.1059,0.0050,0.9012,0.0053</t>
+  </si>
+  <si>
+    <t>0.4981,0.0207,0.4423,0.0056</t>
+  </si>
+  <si>
+    <t>0.0597,0.9676,0.0066,0.0004</t>
   </si>
   <si>
     <t>0.0066,0.9963,0.0015,0.0003</t>
   </si>
   <si>
-    <t>0.1424,0.9134,0.0035,0.0009</t>
-  </si>
-  <si>
-    <t>0.9757,0.0173,0.0043,0.0004</t>
-  </si>
-  <si>
-    <t>0.7367,0.3433,0.0056,0.0009</t>
-  </si>
-  <si>
-    <t>0.1697,0.8107,0.0195,0.0031</t>
-  </si>
-  <si>
-    <t>0.9433,0.0019,0.0298,0.0014</t>
-  </si>
-  <si>
-    <t>0.2485,0.0186,0.7191,0.0229</t>
-  </si>
-  <si>
-    <t>0.1895,0.0015,0.8113,0.0116</t>
-  </si>
-  <si>
-    <t>0.5443,0.0115,0.3615,0.0051</t>
+    <t>0.1426,0.9133,0.0035,0.0009</t>
+  </si>
+  <si>
+    <t>0.9756,0.0174,0.0043,0.0004</t>
+  </si>
+  <si>
+    <t>0.7364,0.3436,0.0056,0.0009</t>
+  </si>
+  <si>
+    <t>0.1700,0.8101,0.0196,0.0031</t>
+  </si>
+  <si>
+    <t>0.9430,0.0019,0.0300,0.0014</t>
+  </si>
+  <si>
+    <t>0.2472,0.0185,0.7207,0.0228</t>
+  </si>
+  <si>
+    <t>0.1889,0.0015,0.8120,0.0116</t>
+  </si>
+  <si>
+    <t>0.5422,0.0114,0.3639,0.0051</t>
   </si>
   <si>
     <t>0.0085,0.0005,0.9939,0.0005</t>
   </si>
   <si>
-    <t>0.0664,0.0038,0.9539,0.0023</t>
-  </si>
-  <si>
-    <t>0.0347,0.0314,0.9423,0.0014</t>
+    <t>0.0659,0.0038,0.9543,0.0023</t>
+  </si>
+  <si>
+    <t>0.0345,0.0313,0.9426,0.0014</t>
   </si>
   <si>
     <t>0.0074,0.0019,0.9931,0.0003</t>
   </si>
   <si>
-    <t>0.0201,0.0101,0.9753,0.0005</t>
-  </si>
-  <si>
-    <t>0.9877,0.0015,0.0043,0.0003</t>
-  </si>
-  <si>
-    <t>0.9668,0.0196,0.0086,0.0019</t>
-  </si>
-  <si>
-    <t>0.9326,0.0539,0.0081,0.0047</t>
+    <t>0.0200,0.0100,0.9753,0.0005</t>
+  </si>
+  <si>
+    <t>0.9876,0.0015,0.0043,0.0003</t>
+  </si>
+  <si>
+    <t>0.9667,0.0196,0.0086,0.0019</t>
+  </si>
+  <si>
+    <t>0.9325,0.0540,0.0082,0.0048</t>
   </si>
   <si>
     <t>0.9851,0.0153,0.0016,0.0011</t>
   </si>
   <si>
-    <t>0.9552,0.0329,0.0114,0.0034</t>
+    <t>0.9551,0.0329,0.0114,0.0034</t>
   </si>
   <si>
     <t>0.9728,0.0241,0.0045,0.0016</t>
   </si>
   <si>
-    <t>0.9751,0.0124,0.0066,0.0018</t>
+    <t>0.9750,0.0124,0.0066,0.0018</t>
   </si>
   <si>
     <t>0.9840,0.0019,0.0065,0.0004</t>
@@ -1480,10 +1486,10 @@
     <t>0.0149,0.0021,0.9912,0.0012</t>
   </si>
   <si>
-    <t>0.1396,0.0279,0.8616,0.0039</t>
-  </si>
-  <si>
-    <t>0.5200,0.0071,0.4683,0.0108</t>
+    <t>0.1386,0.0277,0.8628,0.0039</t>
+  </si>
+  <si>
+    <t>0.5177,0.0070,0.4713,0.0108</t>
   </si>
   <si>
     <t>0.0010,0.0002,0.9992,0.0001</t>
@@ -1492,52 +1498,52 @@
     <t>0.0002,0.0013,0.9994,0.0002</t>
   </si>
   <si>
-    <t>0.0070,0.0301,0.9750,0.0019</t>
+    <t>0.0070,0.0299,0.9751,0.0019</t>
   </si>
   <si>
     <t>0.0001,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0355,0.0079,0.9611,0.0016</t>
+    <t>0.0354,0.0078,0.9612,0.0016</t>
   </si>
   <si>
     <t>0.0043,0.0023,0.9949,0.0005</t>
   </si>
   <si>
-    <t>0.0509,0.0169,0.9339,0.0071</t>
-  </si>
-  <si>
-    <t>0.7669,0.0008,0.2374,0.0022</t>
-  </si>
-  <si>
-    <t>0.3069,0.0007,0.6604,0.0087</t>
-  </si>
-  <si>
-    <t>0.9538,0.0068,0.0184,0.0013</t>
+    <t>0.0507,0.0168,0.9343,0.0071</t>
+  </si>
+  <si>
+    <t>0.7662,0.0008,0.2385,0.0022</t>
+  </si>
+  <si>
+    <t>0.3053,0.0007,0.6626,0.0087</t>
+  </si>
+  <si>
+    <t>0.9536,0.0068,0.0185,0.0013</t>
   </si>
   <si>
     <t>0.9921,0.0046,0.0011,0.0002</t>
   </si>
   <si>
-    <t>0.9796,0.0225,0.0019,0.0010</t>
+    <t>0.9795,0.0225,0.0019,0.0011</t>
   </si>
   <si>
     <t>0.9894,0.0059,0.0020,0.0004</t>
   </si>
   <si>
-    <t>0.9334,0.0535,0.0080,0.0017</t>
-  </si>
-  <si>
-    <t>0.9897,0.0021,0.0027,0.0003</t>
+    <t>0.9333,0.0536,0.0081,0.0017</t>
+  </si>
+  <si>
+    <t>0.9896,0.0021,0.0027,0.0003</t>
   </si>
   <si>
     <t>0.9784,0.0180,0.0032,0.0007</t>
   </si>
   <si>
-    <t>0.9865,0.0124,0.0018,0.0009</t>
-  </si>
-  <si>
-    <t>0.9855,0.0053,0.0034,0.0010</t>
+    <t>0.9865,0.0125,0.0018,0.0009</t>
+  </si>
+  <si>
+    <t>0.9854,0.0053,0.0034,0.0010</t>
   </si>
   <si>
     <t>0.0089,0.0227,0.9809,0.0013</t>
@@ -1549,22 +1555,22 @@
     <t>0.0024,0.0031,0.9972,0.0002</t>
   </si>
   <si>
-    <t>0.0336,0.0227,0.9263,0.0021</t>
+    <t>0.0335,0.0225,0.9266,0.0021</t>
   </si>
   <si>
     <t>0.0235,0.0007,0.9850,0.0005</t>
   </si>
   <si>
-    <t>0.6644,0.0178,0.0986,0.0329</t>
-  </si>
-  <si>
-    <t>0.1013,0.0151,0.8572,0.0119</t>
+    <t>0.6629,0.0177,0.0997,0.0329</t>
+  </si>
+  <si>
+    <t>0.1006,0.0150,0.8585,0.0118</t>
   </si>
   <si>
     <t>0.0041,0.0005,0.9965,0.0008</t>
   </si>
   <si>
-    <t>0.8843,0.0002,0.0099,0.0297</t>
+    <t>0.8839,0.0002,0.0100,0.0296</t>
   </si>
   <si>
     <t>0.0006,0.0018,0.0003,0.9998</t>
@@ -1573,13 +1579,13 @@
     <t>0.0023,0.0004,0.0081,0.9987</t>
   </si>
   <si>
-    <t>0.0000,0.0001,0.0393,0.9998</t>
+    <t>0.0000,0.0001,0.0396,0.9998</t>
   </si>
   <si>
     <t>0.0001,0.0003,0.0018,0.9999</t>
   </si>
   <si>
-    <t>0.6948,0.0037,0.0227,0.2651</t>
+    <t>0.6942,0.0037,0.0228,0.2654</t>
   </si>
 </sst>
 </file>
@@ -1965,7 +1971,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1979,7 +1985,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1993,7 +1999,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2007,7 +2013,7 @@
         <v>265</v>
       </c>
       <c r="D5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2021,7 +2027,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2035,7 +2041,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2049,7 +2055,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2063,7 +2069,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2077,7 +2083,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2091,7 +2097,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2105,7 +2111,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2119,7 +2125,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2133,7 +2139,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2147,7 +2153,7 @@
         <v>266</v>
       </c>
       <c r="D15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2161,7 +2167,7 @@
         <v>266</v>
       </c>
       <c r="D16" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2175,7 +2181,7 @@
         <v>266</v>
       </c>
       <c r="D17" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2186,10 +2192,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D18" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2200,10 +2206,10 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D19" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2214,10 +2220,10 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D20" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2228,10 +2234,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D21" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2242,10 +2248,10 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D22" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2256,10 +2262,10 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D23" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2273,7 +2279,7 @@
         <v>266</v>
       </c>
       <c r="D24" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2287,7 +2293,7 @@
         <v>266</v>
       </c>
       <c r="D25" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2301,7 +2307,7 @@
         <v>266</v>
       </c>
       <c r="D26" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2315,7 +2321,7 @@
         <v>266</v>
       </c>
       <c r="D27" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2329,7 +2335,7 @@
         <v>266</v>
       </c>
       <c r="D28" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2343,7 +2349,7 @@
         <v>266</v>
       </c>
       <c r="D29" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2357,7 +2363,7 @@
         <v>266</v>
       </c>
       <c r="D30" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2371,7 +2377,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2385,7 +2391,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2399,7 +2405,7 @@
         <v>266</v>
       </c>
       <c r="D33" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2413,7 +2419,7 @@
         <v>266</v>
       </c>
       <c r="D34" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2427,7 +2433,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2441,7 +2447,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2452,10 +2458,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D37" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2466,10 +2472,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D38" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2480,10 +2486,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D39" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2497,7 +2503,7 @@
         <v>266</v>
       </c>
       <c r="D40" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2511,7 +2517,7 @@
         <v>266</v>
       </c>
       <c r="D41" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2525,7 +2531,7 @@
         <v>266</v>
       </c>
       <c r="D42" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2539,7 +2545,7 @@
         <v>266</v>
       </c>
       <c r="D43" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2550,10 +2556,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D44" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2567,7 +2573,7 @@
         <v>266</v>
       </c>
       <c r="D45" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2578,10 +2584,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D46" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2592,10 +2598,10 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D47" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2606,10 +2612,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D48" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2620,10 +2626,10 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D49" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2637,7 +2643,7 @@
         <v>266</v>
       </c>
       <c r="D50" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2651,7 +2657,7 @@
         <v>266</v>
       </c>
       <c r="D51" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2665,7 +2671,7 @@
         <v>266</v>
       </c>
       <c r="D52" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2679,7 +2685,7 @@
         <v>266</v>
       </c>
       <c r="D53" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2693,7 +2699,7 @@
         <v>266</v>
       </c>
       <c r="D54" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2707,7 +2713,7 @@
         <v>266</v>
       </c>
       <c r="D55" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2721,7 +2727,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2735,7 +2741,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2749,7 +2755,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2763,7 +2769,7 @@
         <v>266</v>
       </c>
       <c r="D59" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2777,7 +2783,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2791,7 +2797,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2805,7 +2811,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2816,10 +2822,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D63" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2833,7 +2839,7 @@
         <v>266</v>
       </c>
       <c r="D64" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2847,7 +2853,7 @@
         <v>266</v>
       </c>
       <c r="D65" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2858,10 +2864,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D66" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2875,7 +2881,7 @@
         <v>266</v>
       </c>
       <c r="D67" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2886,10 +2892,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D68" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2900,10 +2906,10 @@
         <v>262</v>
       </c>
       <c r="C69" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D69" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2917,7 +2923,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2931,7 +2937,7 @@
         <v>266</v>
       </c>
       <c r="D71" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2945,7 +2951,7 @@
         <v>266</v>
       </c>
       <c r="D72" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2956,10 +2962,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D73" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2970,10 +2976,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D74" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2984,10 +2990,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D75" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2998,10 +3004,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D76" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3015,7 +3021,7 @@
         <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3029,7 +3035,7 @@
         <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3043,7 +3049,7 @@
         <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3057,7 +3063,7 @@
         <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3071,7 +3077,7 @@
         <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3085,7 +3091,7 @@
         <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3096,10 +3102,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D83" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3110,10 +3116,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D84" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3124,10 +3130,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D85" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3138,10 +3144,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D86" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3152,10 +3158,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D87" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3166,10 +3172,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D88" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3183,7 +3189,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3197,7 +3203,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3211,7 +3217,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3225,7 +3231,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3239,7 +3245,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3253,7 +3259,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3267,7 +3273,7 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3281,7 +3287,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3295,7 +3301,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3309,7 +3315,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3323,7 +3329,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3337,7 +3343,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3351,7 +3357,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3365,7 +3371,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3379,7 +3385,7 @@
         <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3393,7 +3399,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3407,7 +3413,7 @@
         <v>266</v>
       </c>
       <c r="D105" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3421,7 +3427,7 @@
         <v>266</v>
       </c>
       <c r="D106" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3435,7 +3441,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3449,7 +3455,7 @@
         <v>266</v>
       </c>
       <c r="D108" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3460,10 +3466,10 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D109" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3474,10 +3480,10 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D110" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3488,10 +3494,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D111" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3502,10 +3508,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D112" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3516,10 +3522,10 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D113" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3530,10 +3536,10 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D114" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3547,7 +3553,7 @@
         <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3561,7 +3567,7 @@
         <v>266</v>
       </c>
       <c r="D116" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3575,7 +3581,7 @@
         <v>266</v>
       </c>
       <c r="D117" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3589,7 +3595,7 @@
         <v>266</v>
       </c>
       <c r="D118" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3603,7 +3609,7 @@
         <v>266</v>
       </c>
       <c r="D119" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3614,10 +3620,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D120" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3628,10 +3634,10 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D121" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3642,10 +3648,10 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D122" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3656,10 +3662,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D123" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3670,10 +3676,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D124" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3684,10 +3690,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D125" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3698,10 +3704,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D126" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3712,10 +3718,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D127" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3729,7 +3735,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3743,7 +3749,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3757,7 +3763,7 @@
         <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3771,7 +3777,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3785,7 +3791,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3799,7 +3805,7 @@
         <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3813,7 +3819,7 @@
         <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3827,7 +3833,7 @@
         <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3838,10 +3844,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D136" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3855,7 +3861,7 @@
         <v>266</v>
       </c>
       <c r="D137" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3869,7 +3875,7 @@
         <v>266</v>
       </c>
       <c r="D138" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3883,7 +3889,7 @@
         <v>266</v>
       </c>
       <c r="D139" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3897,7 +3903,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3908,10 +3914,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="D141" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3925,7 +3931,7 @@
         <v>266</v>
       </c>
       <c r="D142" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3936,10 +3942,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="D143" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3953,7 +3959,7 @@
         <v>265</v>
       </c>
       <c r="D144" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3967,7 +3973,7 @@
         <v>265</v>
       </c>
       <c r="D145" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3981,7 +3987,7 @@
         <v>265</v>
       </c>
       <c r="D146" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3995,7 +4001,7 @@
         <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4006,10 +4012,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D148" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4023,7 +4029,7 @@
         <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4034,10 +4040,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D150" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4051,7 +4057,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4062,10 +4068,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D152" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4079,7 +4085,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4093,7 +4099,7 @@
         <v>266</v>
       </c>
       <c r="D154" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4107,7 +4113,7 @@
         <v>266</v>
       </c>
       <c r="D155" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4121,7 +4127,7 @@
         <v>266</v>
       </c>
       <c r="D156" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4135,7 +4141,7 @@
         <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4149,7 +4155,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4163,7 +4169,7 @@
         <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4177,7 +4183,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4191,7 +4197,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4202,10 +4208,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D162" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4219,7 +4225,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4233,7 +4239,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4247,7 +4253,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4261,7 +4267,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4275,7 +4281,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4289,7 +4295,7 @@
         <v>264</v>
       </c>
       <c r="D168" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4303,7 +4309,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4317,7 +4323,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4331,7 +4337,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4345,7 +4351,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4359,7 +4365,7 @@
         <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4370,10 +4376,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D174" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4387,7 +4393,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4401,7 +4407,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4415,7 +4421,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4429,7 +4435,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4443,7 +4449,7 @@
         <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4457,7 +4463,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4471,7 +4477,7 @@
         <v>266</v>
       </c>
       <c r="D181" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4485,7 +4491,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4499,7 +4505,7 @@
         <v>266</v>
       </c>
       <c r="D183" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4513,7 +4519,7 @@
         <v>266</v>
       </c>
       <c r="D184" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4527,7 +4533,7 @@
         <v>266</v>
       </c>
       <c r="D185" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4541,7 +4547,7 @@
         <v>266</v>
       </c>
       <c r="D186" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4555,7 +4561,7 @@
         <v>266</v>
       </c>
       <c r="D187" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4569,7 +4575,7 @@
         <v>266</v>
       </c>
       <c r="D188" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4583,7 +4589,7 @@
         <v>266</v>
       </c>
       <c r="D189" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4597,7 +4603,7 @@
         <v>266</v>
       </c>
       <c r="D190" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4611,7 +4617,7 @@
         <v>266</v>
       </c>
       <c r="D191" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4622,10 +4628,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="D192" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4639,7 +4645,7 @@
         <v>266</v>
       </c>
       <c r="D193" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4653,7 +4659,7 @@
         <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4667,7 +4673,7 @@
         <v>266</v>
       </c>
       <c r="D195" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4681,7 +4687,7 @@
         <v>266</v>
       </c>
       <c r="D196" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4692,10 +4698,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="D197" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4706,10 +4712,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D198" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4720,10 +4726,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D199" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4734,10 +4740,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D200" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4751,7 +4757,7 @@
         <v>264</v>
       </c>
       <c r="D201" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4765,7 +4771,7 @@
         <v>264</v>
       </c>
       <c r="D202" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4776,10 +4782,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D203" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4793,7 +4799,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4807,7 +4813,7 @@
         <v>266</v>
       </c>
       <c r="D205" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4821,7 +4827,7 @@
         <v>266</v>
       </c>
       <c r="D206" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4835,7 +4841,7 @@
         <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4849,7 +4855,7 @@
         <v>266</v>
       </c>
       <c r="D208" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4863,7 +4869,7 @@
         <v>266</v>
       </c>
       <c r="D209" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4877,7 +4883,7 @@
         <v>266</v>
       </c>
       <c r="D210" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4891,7 +4897,7 @@
         <v>266</v>
       </c>
       <c r="D211" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4905,7 +4911,7 @@
         <v>266</v>
       </c>
       <c r="D212" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4919,7 +4925,7 @@
         <v>264</v>
       </c>
       <c r="D213" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4933,7 +4939,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4947,7 +4953,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4961,7 +4967,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4975,7 +4981,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4989,7 +4995,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5003,7 +5009,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5017,7 +5023,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5031,7 +5037,7 @@
         <v>266</v>
       </c>
       <c r="D221" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5045,7 +5051,7 @@
         <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5059,7 +5065,7 @@
         <v>264</v>
       </c>
       <c r="D223" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5073,7 +5079,7 @@
         <v>266</v>
       </c>
       <c r="D224" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5087,7 +5093,7 @@
         <v>266</v>
       </c>
       <c r="D225" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5101,7 +5107,7 @@
         <v>266</v>
       </c>
       <c r="D226" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5115,7 +5121,7 @@
         <v>266</v>
       </c>
       <c r="D227" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5129,7 +5135,7 @@
         <v>266</v>
       </c>
       <c r="D228" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5143,7 +5149,7 @@
         <v>266</v>
       </c>
       <c r="D229" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5157,7 +5163,7 @@
         <v>266</v>
       </c>
       <c r="D230" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5171,7 +5177,7 @@
         <v>266</v>
       </c>
       <c r="D231" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5185,7 +5191,7 @@
         <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5199,7 +5205,7 @@
         <v>266</v>
       </c>
       <c r="D233" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5213,7 +5219,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5227,7 +5233,7 @@
         <v>264</v>
       </c>
       <c r="D235" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5241,7 +5247,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5255,7 +5261,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5269,7 +5275,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5283,7 +5289,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5297,7 +5303,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5311,7 +5317,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5325,7 +5331,7 @@
         <v>264</v>
       </c>
       <c r="D242" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5339,7 +5345,7 @@
         <v>266</v>
       </c>
       <c r="D243" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5353,7 +5359,7 @@
         <v>266</v>
       </c>
       <c r="D244" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5367,7 +5373,7 @@
         <v>266</v>
       </c>
       <c r="D245" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5381,7 +5387,7 @@
         <v>266</v>
       </c>
       <c r="D246" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5395,7 +5401,7 @@
         <v>266</v>
       </c>
       <c r="D247" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5409,7 +5415,7 @@
         <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5423,7 +5429,7 @@
         <v>266</v>
       </c>
       <c r="D249" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5437,7 +5443,7 @@
         <v>266</v>
       </c>
       <c r="D250" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5451,7 +5457,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5465,7 +5471,7 @@
         <v>265</v>
       </c>
       <c r="D252" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5479,7 +5485,7 @@
         <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5493,7 +5499,7 @@
         <v>265</v>
       </c>
       <c r="D254" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5507,7 +5513,7 @@
         <v>265</v>
       </c>
       <c r="D255" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5521,7 +5527,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
